--- a/0.3.1/StructureDefinition-inera-ehds-encounter.xlsx
+++ b/0.3.1/StructureDefinition-inera-ehds-encounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:34:00+00:00</t>
+    <t>2026-06-24T18:28:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
